--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:17</t>
+    <t xml:space="preserve">2026-09-09 21:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:02</t>
+    <t xml:space="preserve">2026-09-17 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_median_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:51</t>
+    <t xml:space="preserve">2026-10-05 18:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -455,7 +455,7 @@
         <v>2020</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>627126.62</v>
+        <v>627126.63</v>
       </c>
     </row>
     <row r="5">
